--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Mistral-7B-Instruct-v0.3/simple/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Mistral-7B-Instruct-v0.3/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E2">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D3">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="E3">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="G3">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="H3">
         <v>426</v>
